--- a/data_src/xlsx表/条件表.xlsx
+++ b/data_src/xlsx表/条件表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,20 +498,14 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A4" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -521,20 +515,14 @@
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A5" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -544,20 +532,14 @@
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A6" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -567,20 +549,14 @@
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>3001</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="A7" t="n">
+        <v>3001</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -588,6 +564,40 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>情报等级需达到 1 级</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>会员等级需达到 1 级</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data_src/xlsx表/条件表.xlsx
+++ b/data_src/xlsx表/条件表.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,33 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +59,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,191 +453,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>param</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>txt</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>editor_note</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>条件ID</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2章节/3上关通关/5情报等级/6粉丝等级/7持有道具</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>类型对应参数</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>未满足时展示文案</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>策划备注（不进游戏）</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>条件id</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>参数</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>失败文案</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>请先完成第 1 章</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>请先完成第 2 章</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>请先完成第 3 章</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>3001</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>请先完成当前章节前面关卡</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>情报等级需达到 1 级</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>线索等级需达到 1 级</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>线索等级需达到 2 级</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>会员等级需达到 1 级</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
